--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Ratio</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Ratio|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -341,7 +341,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS|1.1.0a</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -573,7 +573,7 @@
     <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/units-of-time</t>
+    <t>http://hl7.org/fhir/ValueSet/units-of-time|4.0.1</t>
   </si>
 </sst>
 </file>
@@ -890,7 +890,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="61.734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.7265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -905,7 +905,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="57.328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.63671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.12890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Ratio|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Ratio</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -341,7 +341,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity}
 </t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -573,7 +573,7 @@
     <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/units-of-time|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/units-of-time</t>
   </si>
 </sst>
 </file>
@@ -890,7 +890,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.7265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -905,7 +905,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="57.328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.63671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
